--- a/medford_duodenoskopy.xlsx
+++ b/medford_duodenoskopy.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Дуоденоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, Fujifilm — всего 9 позиций.</t>
+          <t>Дуоденоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, Fujifilm.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_duodenoskopy.xlsx
+++ b/medford_duodenoskopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать дуоденоскопы для клиники?</t>
+          <t>Чем дуоденоскоп отличается от гастроскопа?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диаметр вводимой трубки, мм, Рабочая длина, мм, Диаметр дистального конца, мм, Глубина резкости, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Дуоденоскоп имеет боковое расположение объектива и подъёмник инструмента (элеватор), которого нет у гастроскопа с прямой оптикой. Боковой обзор выводит большой дуоденальный сосочек в центр кадра, а подъёмник направляет катетер или инструмент под нужным углом к устью протока. Это делает дуоденоскоп основным прибором для ЭРХПГ.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Для чего нужен подъёмник (элеватор)?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Подъёмник — управляемый рычаг у дистального конца, который поднимает и наклоняет вводимый инструмент. Он позволяет точно навести катетер, папиллотом или проводник на устье сосочка при канюляции желчных и панкреатических протоков. Без него прицельная работа при ЭРХПГ практически невозможна.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какой инструментальный канал выбрать?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Olympus, Pentax, Fujifilm. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Для диагностической ЭРХПГ достаточно стандартного канала. Для терапевтических вмешательств — стентирования, литоэкстракции, работы крупным инструментом — нужен канал 4,2 мм, как у Olympus TJF-Q190V и Fujifilm ED-530XT. Диаметр канала определяет, какой инструмент пройдёт через прибор.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Подойдёт ли дуоденоскоп к нашему видеопроцессору?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Дуоденоскоп совместим с видеопроцессором и источником света своего производителя и поколения. Датчик Olympus работает с платформой Olympus, Pentax — с Pentax, Fujifilm — с Fujifilm. Перед покупкой уточните модель процессора в клинике; при замене прибора совпадение разъёма обязательно.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Чем видеодуоденоскоп отличается от фиброскопа?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Видеодуоденоскоп передаёт изображение с матрицы на видеопроцессор и монитор, позволяет вести цифровой архив. Фибродуоденоскоп (например, Pentax FD-34V2) передаёт картинку по оптоволокну напрямую в окуляр. Видеосистемы удобнее для документирования и работы бригады, фиброскопы автономнее.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,120 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение Росздравнадзора?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Да. Дуоденоскоп — медицинское изделие, применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель и убедитесь, что он актуален для планируемой области применения.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>duodenoskopy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Как часто дуоденоскоп нуждается в обслуживании?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Периодичность зависит от нагрузки и рекомендаций производителя. Узел подъёмника и оптический тракт — наиболее ответственные части, требующие контроля герметичности и целостности. Регулярная проверка каналов и своевременный ремонт продлевают ресурс прибора; график обслуживания согласуют с сервисной службой.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>duodenoskopy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Что важно в обработке дуоденоскопа?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Конструкция дистального конца с подъёмником имеет труднодоступные зоны, поэтому протокол включает ручную очистку канала подъёмника перед машинной дезинфекцией. Выбранная модель должна быть совместима с моюще-дезинфицирующей машиной клиники. Соблюдение протокола снижает риск перекрёстной контаминации.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>duodenoskopy</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Дуоденоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, Fujifilm.</t>
+          <t>Дуоденоскопы — гибкие эндоскопы бокового обзора с подъёмником инструмента для ретроградной холангиопанкреатографии (ЭРХПГ) и вмешательств на большом дуоденальном сосочке. В каталоге представлены модели Olympus, Pentax и Fujifilm с диаметром дистального конца 13,0–13,7 мм и вводимой трубки 11,3–11,6 мм. Рабочая длина составляет 1240–1550 мм, глубина резкости — 4–60 мм, угол поля зрения — 98–100°. Терапевтические версии несут инструментальный канал 4,2 мм под крупный инструментарий.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Дуоденоскопы в каталоге: характеристики по моделям</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое дуоденоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3619,21 +3733,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Дуоденоскопы в каталоге: характеристики по моделям</t>
         </is>
       </c>
     </row>
@@ -3645,12 +3759,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Дистальный конец, мм</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр вводимой трубки, мм</t>
+          <t>Вводимая трубка, мм</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3660,52 +3774,56 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр дистального конца, мм</t>
+          <t>Инстр. канал, мм</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Глубина резкости, мм</t>
+          <t>Угол обзора, °</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеодуоденоскоп ED-5GT</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Olympus TJF-Q180V</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>13,7</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>11,3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Видеодуоденоскоп Olympus TJF-Q180V</t>
+          <t>Olympus TJF-Q190V</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3720,24 +3838,24 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>5-60</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеодуоденоскоп Pentax ED34-i10T2</t>
+          <t>Pentax ED34-i10T2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3752,61 +3870,61 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>13,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4-60</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Терапевтический видеодуоденоскоп Fujifilm ED-530XT</t>
+          <t>Pentax ED34-i10T</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fujifilm</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>11,5</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4-60</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Видеодуоденоскоп Fujifilm ED-580XT</t>
+          <t>Pentax ED-3490TK</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Fujifilm</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>11,3</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -3816,44 +3934,76 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>4-60</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Видеодуоденоскоп Olympus TJF-Q190V</t>
+          <t>Fujifilm ED-530XT</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>11,5</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Fujifilm ED-580XT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>13,1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>5-60</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -3871,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4197,12 +4347,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип вмешательств</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается дуоденоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Диагностическая ЭРХПГ и терапевтические процедуры предъявляют разные требования к каналу. Для стентирования, литоэкстракции и работы крупным инструментом нужен инструментальный канал 4,2 мм — он есть у терапевтических версий Olympus TJF-Q190V и Fujifilm ED-530XT. Для базовой диагностики подойдёт стандартный канал.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4242,12 +4392,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте совместимость с видеосистемой</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Дуоденоскоп подключается к видеопроцессору своего производителя. Уточните модель процессора и источника света в клинике: датчик Olympus работает с платформой Olympus, Pentax — с Pentax, Fujifilm — с Fujifilm. Замена в существующую стойку требует совпадения разъёма и поколения системы.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4287,12 +4437,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сопоставьте геометрию дистального конца</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диаметр вводимой трубки, мм, Рабочая длина, мм, Диаметр дистального конца, мм, Глубина резкости, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Диаметр дистального конца в каталоге 13,0–13,7 мм, вводимой трубки — 11,3–11,6 мм. Меньший диаметр облегчает интубацию у пациентов со сложной анатомией. Оцените рабочую длину: у большинства моделей 1240–1250 мм, у Fujifilm ED-530XT — 1550 мм.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4332,12 +4482,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените оптику</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Olympus, Pentax, Fujifilm.</t>
+          <t>Угол поля зрения у моделей 98–100°, глубина резкости 4–60 мм. Боковой обзор выводит устье большого дуоденального сосочка в центр кадра, что критично для канюляции. Видеомодели дают цифровое изображение для архива, фиброскопы (Pentax FD-34V2) — прямую оптическую передачу.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4377,12 +4527,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Заложите протокол обработки</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Подъёмник и его канал — зона, требующая ручной очистки перед машинной дезинфекцией. Согласуйте выбранную модель с имеющейся моюще-дезинфицирующей машиной и щётками. Учтите наличие расходников и запасных дистальных колпачков в эксплуатации.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4422,12 +4572,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте регистрацию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Убедитесь, что модель имеет действующее регистрационное удостоверение Росздравнадзора для применения в РФ. Уточните доступность ремонта подъёмного механизма и оптического тракта, а также сроки поставки запасных частей для выбранного бренда.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4477,7 +4627,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Дуоденоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Olympus, Pentax, Fujifilm. При выборе обращают внимание на диаметр вводимой трубки, рабочая длина, диаметр дистального конца, глубина резкости, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Дуоденоскоп выбирают по трём точкам: боковой обзор и надёжность подъёмника, диаметр инструментального канала и совместимость с уже установленным видеопроцессором. Терапевтический канал 4,2 мм нужен там, где идёт стентирование и литоэкстракция крупным инструментом; для диагностической ЭРХПГ достаточно стандартного. Отдельный вопрос — обработка: конструкция дистального конца с подъёмником требует строгого протокола очистки, и это стоит закладывать в эксплуатацию сразу.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4761,13 +4911,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое дуоденоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Дуоденоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Olympus, Pentax, Fujifilm. Подберём вариант под задачи вашего отделения.</t>
+          <t>Дуоденоскоп — гибкий эндоскоп с боковой оптикой и подъёмником (элеватором) для проведения ЭРХПГ, стентирования желчных протоков и удаления камней. Отличается от гастроскопа боковым расположением объектива и управляемым подъёмником, который направляет инструмент к устью сосочка. В каталоге модели Olympus, Pentax и Fujifilm: диаметр дистального конца 13,0–13,7 мм, рабочая длина 1240–1550 мм, инструментальный канал терапевтических версий 4,2 мм. Выбор модели зависит от совместимости с видеосистемой клиники и планируемых вмешательств.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4804,13 +4954,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое дуоденоскоп и где он применяется</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диаметр вводимой трубки, мм, Рабочая длина, мм, Диаметр дистального конца, мм, Глубина резкости, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Дуоденоскоп — гибкий эндоскоп бокового обзора, предназначенный для осмотра двенадцатиперстной кишки и большого дуоденального сосочка. Основная область применения — эндоскопическая ретроградная холангиопанкреатография (ЭРХПГ): контрастирование, стентирование и дренирование желчных и панкреатических протоков, удаление конкрементов. Боковая оптика и подъёмник инструмента отличают прибор от гастроскопа и делают его специализированным инструментом гепатобилиарной эндоскопии.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4847,13 +4997,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Ключевые характеристики при подборе</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные параметры дуоденоскопа: диаметр дистального конца (13,0–13,7 мм), диаметр вводимой трубки (11,3–11,6 мм), рабочая длина (1240–1550 мм), глубина резкости (4–60 мм), угол поля зрения (98–100°) и диаметр инструментального канала. Терапевтические модели с каналом 4,2 мм рассчитаны на крупный инструмент. Меньший диаметр вводимой трубки облегчает проведение прибора при сложной анатомии.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4890,13 +5040,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Бренды и модели в каталоге</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>В каталоге представлены дуоденоскопы Olympus (TJF-Q180V, TJF-Q190V), Pentax (ED34-i10T2, ED34-i10T, ED-3490TK, фиброскоп FD-34V2) и Fujifilm (ED-530XT, ED-580XT). Модели различаются диаметрами, рабочей длиной и наличием терапевтического канала. Каждый бренд работает со своей видеосистемой, поэтому подбор ведут с учётом уже установленного в клинике процессора и источника света.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4913,6 +5063,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Видеодуоденоскоп или фиброскоп</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Видеодуоденоскопы передают изображение на видеопроцессор и монитор, поддерживают цифровой архив и совместную работу бригады. Фибродуоденоскопы передают картинку по оптоволокну в окуляр и не требуют видеостойки. Выбор зависит от оснащения кабинета: при наличии видеосистемы логичны видеомодели, для автономной работы или ограниченного бюджета рассматривают фиброскопы.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>duodenoskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
